--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/calculadora-pricing-eventos-parrillero.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/calculadora-pricing-eventos-parrillero.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ejemplos'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -505,7 +507,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -532,6 +534,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -633,6 +636,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -648,7 +652,7 @@
       </c>
       <c r="B16" s="6">
         <f>IF(B10=1,9,IF(B10=2,14,22))</f>
-        <v/>
+        <v>14.0</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +673,7 @@
       </c>
       <c r="B18" s="6">
         <f>IF(B12=1,8,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -680,7 +684,7 @@
       </c>
       <c r="B19" s="6">
         <f>IF(B13=1,2,IF(B13=2,1.5,0))</f>
-        <v/>
+        <v>2.0</v>
       </c>
     </row>
     <row r="20">
@@ -701,7 +705,7 @@
       </c>
       <c r="B21" s="6">
         <f>B8*2*0.18</f>
-        <v/>
+        <v>12.6</v>
       </c>
     </row>
     <row r="22">
@@ -712,7 +716,7 @@
       </c>
       <c r="B22" s="6">
         <f>B11*100</f>
-        <v/>
+        <v>100.0</v>
       </c>
     </row>
     <row r="23">
@@ -733,7 +737,7 @@
       </c>
       <c r="B24" s="6">
         <f>(B16+B17+B18+B19)*B6</f>
-        <v/>
+        <v>1560.0</v>
       </c>
     </row>
     <row r="25">
@@ -744,7 +748,7 @@
       </c>
       <c r="B25" s="6">
         <f>B20+B21+B22+B23</f>
-        <v/>
+        <v>162.6</v>
       </c>
     </row>
     <row r="26">
@@ -755,9 +759,10 @@
       </c>
       <c r="B26" s="6">
         <f>B24+B25</f>
-        <v/>
-      </c>
-    </row>
+        <v>1722.6</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
@@ -783,7 +788,7 @@
       </c>
       <c r="B30" s="6">
         <f>B26/B6</f>
-        <v/>
+        <v>21.5325</v>
       </c>
     </row>
     <row r="31">
@@ -794,7 +799,7 @@
       </c>
       <c r="B31" s="6">
         <f>IF(B5="B2C particular (boda finca / cumpleaños)",B30/(1-B29),B30/(1-(B29+0.10)))</f>
-        <v/>
+        <v>47.85</v>
       </c>
     </row>
     <row r="32">
@@ -805,7 +810,7 @@
       </c>
       <c r="B32" s="6">
         <f>IF(B8&gt;30,(B8-30)*1.2+150,0)</f>
-        <v/>
+        <v>156.0</v>
       </c>
     </row>
     <row r="33">
@@ -816,7 +821,7 @@
       </c>
       <c r="B33" s="8">
         <f>B6*B31+B32</f>
-        <v/>
+        <v>3984.0</v>
       </c>
     </row>
     <row r="34">
@@ -827,7 +832,7 @@
       </c>
       <c r="B34" s="6">
         <f>B33/B6</f>
-        <v/>
+        <v>49.8</v>
       </c>
     </row>
     <row r="35">
@@ -838,7 +843,7 @@
       </c>
       <c r="B35" s="8">
         <f>B33-B26</f>
-        <v/>
+        <v>2261.4</v>
       </c>
     </row>
     <row r="36">
@@ -849,18 +854,27 @@
       </c>
       <c r="B36" s="9">
         <f>B35/B33</f>
-        <v/>
+        <v>0.5676204819277109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -868,7 +882,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -897,6 +911,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1284,6 +1299,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>